--- a/data/trans_dic/IP31KM14_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM14_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 17,6</t>
+          <t>5,09; 20,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 18,29</t>
+          <t>2,06; 12,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 15,27</t>
+          <t>4,61; 12,82</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 13,56</t>
+          <t>9,67; 22,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,56; 21,86</t>
+          <t>5,68; 15,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 16,0</t>
+          <t>9,0; 17,45</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,51; 26,23</t>
+          <t>8,32; 22,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 23,46</t>
+          <t>10,18; 26,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,98; 21,88</t>
+          <t>10,68; 21,74</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,45; 29,33</t>
+          <t>14,43; 41,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,44; 38,49</t>
+          <t>13,54; 31,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,09; 30,71</t>
+          <t>16,68; 32,15</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,73</t>
+          <t>4,19; 18,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 17,49</t>
+          <t>0,0; 9,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,78</t>
+          <t>3,02; 11,31</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,36; 25,27</t>
+          <t>6,98; 23,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 20,51</t>
+          <t>8,05; 25,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,63; 19,5</t>
+          <t>9,2; 20,55</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,67; 44,01</t>
+          <t>28,28; 43,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,08; 47,37</t>
+          <t>26,51; 40,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,88; 42,92</t>
+          <t>28,96; 39,89</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,93; 26,6</t>
+          <t>7,54; 16,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 17,28</t>
+          <t>13,8; 27,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,47; 18,96</t>
+          <t>11,7; 19,42</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,46; 20,53</t>
+          <t>16,12; 21,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,24; 22,69</t>
+          <t>15,42; 20,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,22; 20,61</t>
+          <t>16,48; 20,37</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>9364</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1588; 12564</t>
+          <t>3070; 12332</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3804; 13643</t>
+          <t>1131; 6785</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7066; 22301</t>
+          <t>5309; 14769</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19226</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29240</t>
+          <t>27153</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3970; 17038</t>
+          <t>11111; 25878</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12090; 27632</t>
+          <t>5644; 15824</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17740; 40323</t>
+          <t>19290; 37399</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>17261</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5838; 14569</t>
+          <t>4766; 12923</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5502; 15166</t>
+          <t>5508; 14144</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13190; 26294</t>
+          <t>11901; 24224</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14370</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33069</t>
+          <t>33213</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8678; 20436</t>
+          <t>10075; 28706</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10126; 29007</t>
+          <t>9538; 22074</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21890; 44540</t>
+          <t>23394; 45106</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4873</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3671</t>
+          <t>1659; 7329</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1509; 7122</t>
+          <t>0; 3365</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2275; 8824</t>
+          <t>2261; 8479</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>12735</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3704; 11191</t>
+          <t>3297; 10989</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3004; 11029</t>
+          <t>3565; 11262</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8467; 19119</t>
+          <t>8420; 18798</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>43198</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>57377</t>
+          <t>41070</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100575</t>
+          <t>90501</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34221; 54443</t>
+          <t>39760; 61408</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>46641; 73446</t>
+          <t>32298; 49850</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>86088; 119626</t>
+          <t>75995; 104664</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>24642</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43009</t>
+          <t>44951</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17918; 34221</t>
+          <t>11848; 25212</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12517; 26643</t>
+          <t>19036; 37890</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32453; 53623</t>
+          <t>34524; 57288</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>157</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>114180</t>
+          <t>127855</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>141210</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>255390</t>
+          <t>240050</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>94435; 134058</t>
+          <t>110698; 148862</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>120956; 168997</t>
+          <t>95356; 129370</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>226784; 288156</t>
+          <t>215056; 265890</t>
         </is>
       </c>
     </row>
